--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 7.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 7.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Penjualan 7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Penjualan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF418E5-740E-46D0-B4D2-9FF57417B007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -380,7 +379,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -621,6 +620,12 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -630,19 +635,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
     <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 2 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -919,7 +918,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6216CEB9-BAB9-4A1A-81FA-F8472AE5D4DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -1697,16 +1696,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
     </row>
     <row r="2" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
@@ -1744,11 +1743,26 @@
       <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="E3" s="29" t="str">
+        <f>IF(LEFT(D3,1)="Y","Yamaha",IF(LEFT(D3,1)="K","Kawasaki",IF(LEFT(D3,1)="H","Honda")))</f>
+        <v>Yamaha</v>
+      </c>
+      <c r="F3" s="30" t="str">
+        <f>VLOOKUP(MID(D3,2,2),$B$18:$E$27,1,FALSE)</f>
+        <v>JU</v>
+      </c>
+      <c r="G3" s="31" t="str">
+        <f>VLOOKUP(MID(D3,2,2),$B$18:$E$27,2,FALSE)</f>
+        <v>Jupiter</v>
+      </c>
+      <c r="H3" s="32">
+        <f>VLOOKUP(MID(D3,2,2),$B$18:$E$27,3,FALSE)</f>
+        <v>1750000</v>
+      </c>
+      <c r="I3" s="32">
+        <f>VLOOKUP(MID(D3,2,2),$B$18:$E$27,4,FALSE)</f>
+        <v>608000</v>
+      </c>
       <c r="J3" s="4"/>
       <c r="K3" s="5" t="s">
         <v>8</v>
@@ -1764,24 +1778,39 @@
       <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="K4" s="34">
+      <c r="E4" s="29" t="str">
+        <f t="shared" ref="E4:E15" si="0">IF(LEFT(D4,1)="Y","Yamaha",IF(LEFT(D4,1)="K","Kawasaki",IF(LEFT(D4,1)="H","Honda")))</f>
+        <v>Kawasaki</v>
+      </c>
+      <c r="F4" s="30" t="str">
+        <f t="shared" ref="F4:F15" si="1">VLOOKUP(MID(D4,2,2),$B$18:$E$27,1,FALSE)</f>
+        <v>NJ</v>
+      </c>
+      <c r="G4" s="31" t="str">
+        <f t="shared" ref="G4:G15" si="2">VLOOKUP(MID(D4,2,2),$B$18:$E$27,2,FALSE)</f>
+        <v>Ninja 250</v>
+      </c>
+      <c r="H4" s="32">
+        <f t="shared" ref="H4:H15" si="3">VLOOKUP(MID(D4,2,2),$B$18:$E$27,3,FALSE)</f>
+        <v>15000000</v>
+      </c>
+      <c r="I4" s="32">
+        <f t="shared" ref="I4:I15" si="4">VLOOKUP(MID(D4,2,2),$B$18:$E$27,4,FALSE)</f>
+        <v>1875000</v>
+      </c>
+      <c r="K4" s="36">
         <v>1</v>
       </c>
-      <c r="L4" s="35" t="s">
+      <c r="L4" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
     </row>
     <row r="5" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
@@ -1793,20 +1822,35 @@
       <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
+      <c r="E5" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v>Honda</v>
+      </c>
+      <c r="F5" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>KR</v>
+      </c>
+      <c r="G5" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>Kharisma</v>
+      </c>
+      <c r="H5" s="32">
+        <f t="shared" si="3"/>
+        <v>1200000</v>
+      </c>
+      <c r="I5" s="32">
+        <f t="shared" si="4"/>
+        <v>652000</v>
+      </c>
+      <c r="K5" s="36"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
     </row>
     <row r="6" spans="2:19" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
@@ -1818,24 +1862,39 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="K6" s="34">
+      <c r="E6" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v>Honda</v>
+      </c>
+      <c r="F6" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>SX</v>
+      </c>
+      <c r="G6" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>Supra X</v>
+      </c>
+      <c r="H6" s="32">
+        <f t="shared" si="3"/>
+        <v>2000000</v>
+      </c>
+      <c r="I6" s="32">
+        <f t="shared" si="4"/>
+        <v>531000</v>
+      </c>
+      <c r="K6" s="36">
         <v>2</v>
       </c>
-      <c r="L6" s="35" t="s">
+      <c r="L6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="S6" s="37"/>
     </row>
     <row r="7" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
@@ -1847,20 +1906,35 @@
       <c r="D7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
+      <c r="E7" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v>Yamaha</v>
+      </c>
+      <c r="F7" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>RK</v>
+      </c>
+      <c r="G7" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>RX King</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" si="3"/>
+        <v>2500000</v>
+      </c>
+      <c r="I7" s="32">
+        <f t="shared" si="4"/>
+        <v>711000</v>
+      </c>
+      <c r="K7" s="36"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
     </row>
     <row r="8" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3">
@@ -1872,11 +1946,26 @@
       <c r="D8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="E8" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v>Yamaha</v>
+      </c>
+      <c r="F8" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>VR</v>
+      </c>
+      <c r="G8" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>Vega R</v>
+      </c>
+      <c r="H8" s="32">
+        <f t="shared" si="3"/>
+        <v>1250000</v>
+      </c>
+      <c r="I8" s="32">
+        <f t="shared" si="4"/>
+        <v>481000</v>
+      </c>
       <c r="K8" s="25">
         <v>3</v>
       </c>
@@ -1894,11 +1983,26 @@
       <c r="D9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="E9" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v>Honda</v>
+      </c>
+      <c r="F9" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>SF</v>
+      </c>
+      <c r="G9" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>Supra Fit</v>
+      </c>
+      <c r="H9" s="32">
+        <f t="shared" si="3"/>
+        <v>1750000</v>
+      </c>
+      <c r="I9" s="32">
+        <f t="shared" si="4"/>
+        <v>566000</v>
+      </c>
       <c r="K9" s="25">
         <v>4</v>
       </c>
@@ -1916,11 +2020,26 @@
       <c r="D10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="E10" s="29" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>TG</v>
+      </c>
+      <c r="G10" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>Tiger</v>
+      </c>
+      <c r="H10" s="32">
+        <f t="shared" si="3"/>
+        <v>3000000</v>
+      </c>
+      <c r="I10" s="32">
+        <f t="shared" si="4"/>
+        <v>915000</v>
+      </c>
       <c r="K10" s="6"/>
       <c r="L10" s="7"/>
     </row>
@@ -1934,11 +2053,26 @@
       <c r="D11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="E11" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v>Honda</v>
+      </c>
+      <c r="F11" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>TG</v>
+      </c>
+      <c r="G11" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>Tiger</v>
+      </c>
+      <c r="H11" s="32">
+        <f t="shared" si="3"/>
+        <v>3000000</v>
+      </c>
+      <c r="I11" s="32">
+        <f t="shared" si="4"/>
+        <v>915000</v>
+      </c>
     </row>
     <row r="12" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3">
@@ -1950,11 +2084,26 @@
       <c r="D12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
+      <c r="E12" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v>Yamaha</v>
+      </c>
+      <c r="F12" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>MI</v>
+      </c>
+      <c r="G12" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>Mio</v>
+      </c>
+      <c r="H12" s="32">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="I12" s="32">
+        <f t="shared" si="4"/>
+        <v>504000</v>
+      </c>
     </row>
     <row r="13" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3">
@@ -1966,11 +2115,26 @@
       <c r="D13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
+      <c r="E13" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v>Honda</v>
+      </c>
+      <c r="F13" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>KR</v>
+      </c>
+      <c r="G13" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>Kharisma</v>
+      </c>
+      <c r="H13" s="32">
+        <f t="shared" si="3"/>
+        <v>1200000</v>
+      </c>
+      <c r="I13" s="32">
+        <f t="shared" si="4"/>
+        <v>652000</v>
+      </c>
     </row>
     <row r="14" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3">
@@ -1982,11 +2146,26 @@
       <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
+      <c r="E14" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v>Yamaha</v>
+      </c>
+      <c r="F14" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>JU</v>
+      </c>
+      <c r="G14" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>Jupiter</v>
+      </c>
+      <c r="H14" s="32">
+        <f t="shared" si="3"/>
+        <v>1750000</v>
+      </c>
+      <c r="I14" s="32">
+        <f t="shared" si="4"/>
+        <v>608000</v>
+      </c>
     </row>
     <row r="15" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3">
@@ -1998,11 +2177,26 @@
       <c r="D15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
+      <c r="E15" s="29" t="str">
+        <f t="shared" si="0"/>
+        <v>Honda</v>
+      </c>
+      <c r="F15" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>SX</v>
+      </c>
+      <c r="G15" s="31" t="str">
+        <f t="shared" si="2"/>
+        <v>Supra X</v>
+      </c>
+      <c r="H15" s="32">
+        <f t="shared" si="3"/>
+        <v>2000000</v>
+      </c>
+      <c r="I15" s="32">
+        <f t="shared" si="4"/>
+        <v>531000</v>
+      </c>
     </row>
     <row r="16" spans="2:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I16" s="8"/>
@@ -2031,11 +2225,11 @@
         <v>27</v>
       </c>
       <c r="F18" s="14"/>
-      <c r="G18" s="36" t="s">
+      <c r="G18" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
     </row>
     <row r="19" spans="2:12" ht="15" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
@@ -2051,11 +2245,11 @@
         <v>608000</v>
       </c>
       <c r="F19" s="17"/>
-      <c r="G19" s="37" t="s">
+      <c r="G19" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
     </row>
@@ -2198,7 +2392,7 @@
     <mergeCell ref="L6:S7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G19" r:id="rId1" xr:uid="{69C3C31B-2F65-46DB-91ED-5BFD4695DA71}"/>
+    <hyperlink ref="G19" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 7.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 7.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Penjualan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Penjualan 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF418E5-740E-46D0-B4D2-9FF57417B007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -379,7 +380,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -620,12 +621,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -635,13 +630,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
     <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="2"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -918,7 +919,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6216CEB9-BAB9-4A1A-81FA-F8472AE5D4DE}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -1696,16 +1697,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
@@ -1743,26 +1744,11 @@
       <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="29" t="str">
-        <f>IF(LEFT(D3,1)="Y","Yamaha",IF(LEFT(D3,1)="K","Kawasaki",IF(LEFT(D3,1)="H","Honda")))</f>
-        <v>Yamaha</v>
-      </c>
-      <c r="F3" s="30" t="str">
-        <f>VLOOKUP(MID(D3,2,2),$B$18:$E$27,1,FALSE)</f>
-        <v>JU</v>
-      </c>
-      <c r="G3" s="31" t="str">
-        <f>VLOOKUP(MID(D3,2,2),$B$18:$E$27,2,FALSE)</f>
-        <v>Jupiter</v>
-      </c>
-      <c r="H3" s="32">
-        <f>VLOOKUP(MID(D3,2,2),$B$18:$E$27,3,FALSE)</f>
-        <v>1750000</v>
-      </c>
-      <c r="I3" s="32">
-        <f>VLOOKUP(MID(D3,2,2),$B$18:$E$27,4,FALSE)</f>
-        <v>608000</v>
-      </c>
+      <c r="E3" s="29"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="J3" s="4"/>
       <c r="K3" s="5" t="s">
         <v>8</v>
@@ -1778,39 +1764,24 @@
       <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="29" t="str">
-        <f t="shared" ref="E4:E15" si="0">IF(LEFT(D4,1)="Y","Yamaha",IF(LEFT(D4,1)="K","Kawasaki",IF(LEFT(D4,1)="H","Honda")))</f>
-        <v>Kawasaki</v>
-      </c>
-      <c r="F4" s="30" t="str">
-        <f t="shared" ref="F4:F15" si="1">VLOOKUP(MID(D4,2,2),$B$18:$E$27,1,FALSE)</f>
-        <v>NJ</v>
-      </c>
-      <c r="G4" s="31" t="str">
-        <f t="shared" ref="G4:G15" si="2">VLOOKUP(MID(D4,2,2),$B$18:$E$27,2,FALSE)</f>
-        <v>Ninja 250</v>
-      </c>
-      <c r="H4" s="32">
-        <f t="shared" ref="H4:H15" si="3">VLOOKUP(MID(D4,2,2),$B$18:$E$27,3,FALSE)</f>
-        <v>15000000</v>
-      </c>
-      <c r="I4" s="32">
-        <f t="shared" ref="I4:I15" si="4">VLOOKUP(MID(D4,2,2),$B$18:$E$27,4,FALSE)</f>
-        <v>1875000</v>
-      </c>
-      <c r="K4" s="36">
+      <c r="E4" s="29"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="K4" s="34">
         <v>1</v>
       </c>
-      <c r="L4" s="37" t="s">
+      <c r="L4" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
     </row>
     <row r="5" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
@@ -1822,35 +1793,20 @@
       <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v>Honda</v>
-      </c>
-      <c r="F5" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>KR</v>
-      </c>
-      <c r="G5" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>Kharisma</v>
-      </c>
-      <c r="H5" s="32">
-        <f t="shared" si="3"/>
-        <v>1200000</v>
-      </c>
-      <c r="I5" s="32">
-        <f t="shared" si="4"/>
-        <v>652000</v>
-      </c>
-      <c r="K5" s="36"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="35"/>
     </row>
     <row r="6" spans="2:19" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
@@ -1862,39 +1818,24 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v>Honda</v>
-      </c>
-      <c r="F6" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>SX</v>
-      </c>
-      <c r="G6" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>Supra X</v>
-      </c>
-      <c r="H6" s="32">
-        <f t="shared" si="3"/>
-        <v>2000000</v>
-      </c>
-      <c r="I6" s="32">
-        <f t="shared" si="4"/>
-        <v>531000</v>
-      </c>
-      <c r="K6" s="36">
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="K6" s="34">
         <v>2</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="37"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
     </row>
     <row r="7" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
@@ -1906,35 +1847,20 @@
       <c r="D7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v>Yamaha</v>
-      </c>
-      <c r="F7" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>RK</v>
-      </c>
-      <c r="G7" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>RX King</v>
-      </c>
-      <c r="H7" s="32">
-        <f t="shared" si="3"/>
-        <v>2500000</v>
-      </c>
-      <c r="I7" s="32">
-        <f t="shared" si="4"/>
-        <v>711000</v>
-      </c>
-      <c r="K7" s="36"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="37"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
     </row>
     <row r="8" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3">
@@ -1946,26 +1872,11 @@
       <c r="D8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v>Yamaha</v>
-      </c>
-      <c r="F8" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>VR</v>
-      </c>
-      <c r="G8" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>Vega R</v>
-      </c>
-      <c r="H8" s="32">
-        <f t="shared" si="3"/>
-        <v>1250000</v>
-      </c>
-      <c r="I8" s="32">
-        <f t="shared" si="4"/>
-        <v>481000</v>
-      </c>
+      <c r="E8" s="29"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
       <c r="K8" s="25">
         <v>3</v>
       </c>
@@ -1983,26 +1894,11 @@
       <c r="D9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v>Honda</v>
-      </c>
-      <c r="F9" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>SF</v>
-      </c>
-      <c r="G9" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>Supra Fit</v>
-      </c>
-      <c r="H9" s="32">
-        <f t="shared" si="3"/>
-        <v>1750000</v>
-      </c>
-      <c r="I9" s="32">
-        <f t="shared" si="4"/>
-        <v>566000</v>
-      </c>
+      <c r="E9" s="29"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
       <c r="K9" s="25">
         <v>4</v>
       </c>
@@ -2020,26 +1916,11 @@
       <c r="D10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="29" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>TG</v>
-      </c>
-      <c r="G10" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>Tiger</v>
-      </c>
-      <c r="H10" s="32">
-        <f t="shared" si="3"/>
-        <v>3000000</v>
-      </c>
-      <c r="I10" s="32">
-        <f t="shared" si="4"/>
-        <v>915000</v>
-      </c>
+      <c r="E10" s="29"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
       <c r="K10" s="6"/>
       <c r="L10" s="7"/>
     </row>
@@ -2053,26 +1934,11 @@
       <c r="D11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v>Honda</v>
-      </c>
-      <c r="F11" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>TG</v>
-      </c>
-      <c r="G11" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>Tiger</v>
-      </c>
-      <c r="H11" s="32">
-        <f t="shared" si="3"/>
-        <v>3000000</v>
-      </c>
-      <c r="I11" s="32">
-        <f t="shared" si="4"/>
-        <v>915000</v>
-      </c>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
     </row>
     <row r="12" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3">
@@ -2084,26 +1950,11 @@
       <c r="D12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v>Yamaha</v>
-      </c>
-      <c r="F12" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>MI</v>
-      </c>
-      <c r="G12" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>Mio</v>
-      </c>
-      <c r="H12" s="32">
-        <f t="shared" si="3"/>
-        <v>1500000</v>
-      </c>
-      <c r="I12" s="32">
-        <f t="shared" si="4"/>
-        <v>504000</v>
-      </c>
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
     </row>
     <row r="13" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3">
@@ -2115,26 +1966,11 @@
       <c r="D13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v>Honda</v>
-      </c>
-      <c r="F13" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>KR</v>
-      </c>
-      <c r="G13" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>Kharisma</v>
-      </c>
-      <c r="H13" s="32">
-        <f t="shared" si="3"/>
-        <v>1200000</v>
-      </c>
-      <c r="I13" s="32">
-        <f t="shared" si="4"/>
-        <v>652000</v>
-      </c>
+      <c r="E13" s="29"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
     </row>
     <row r="14" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3">
@@ -2146,26 +1982,11 @@
       <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v>Yamaha</v>
-      </c>
-      <c r="F14" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>JU</v>
-      </c>
-      <c r="G14" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>Jupiter</v>
-      </c>
-      <c r="H14" s="32">
-        <f t="shared" si="3"/>
-        <v>1750000</v>
-      </c>
-      <c r="I14" s="32">
-        <f t="shared" si="4"/>
-        <v>608000</v>
-      </c>
+      <c r="E14" s="29"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
     </row>
     <row r="15" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3">
@@ -2177,26 +1998,11 @@
       <c r="D15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v>Honda</v>
-      </c>
-      <c r="F15" s="30" t="str">
-        <f t="shared" si="1"/>
-        <v>SX</v>
-      </c>
-      <c r="G15" s="31" t="str">
-        <f t="shared" si="2"/>
-        <v>Supra X</v>
-      </c>
-      <c r="H15" s="32">
-        <f t="shared" si="3"/>
-        <v>2000000</v>
-      </c>
-      <c r="I15" s="32">
-        <f t="shared" si="4"/>
-        <v>531000</v>
-      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
     </row>
     <row r="16" spans="2:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I16" s="8"/>
@@ -2225,11 +2031,11 @@
         <v>27</v>
       </c>
       <c r="F18" s="14"/>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
     </row>
     <row r="19" spans="2:12" ht="15" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
@@ -2245,11 +2051,11 @@
         <v>608000</v>
       </c>
       <c r="F19" s="17"/>
-      <c r="G19" s="34" t="s">
+      <c r="G19" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
     </row>
@@ -2392,7 +2198,7 @@
     <mergeCell ref="L6:S7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G19" r:id="rId1"/>
+    <hyperlink ref="G19" r:id="rId1" xr:uid="{69C3C31B-2F65-46DB-91ED-5BFD4695DA71}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
